--- a/stories/arbres/TREE-SOC-002.xlsx
+++ b/stories/arbres/TREE-SOC-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila est dans la cuisine, avec papa. On va sortir. Papa dit : dans la voiture, on reste assis, avec l'adulte. Lila s'assoit déjà sur la chaise. Les fesses sont sur l'assise. Les pieds sont par terre. Les mains tiennent le doudou. Papa est l'adulte, tout près. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
+          <t>Lila est dans la cuisine, avec papa. On va sortir. Dans la voiture, on reste assis, avec l'adulte. Lila s'assoit déjà sur la chaise. Les fesses sont sur l'assise. Les pieds sont par terre. Les mains tiennent le doudou. Papa est l'adulte, tout près. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est dans la cuisine, avec papa. On va sortir.
+papa|Dans la voiture, on reste assis, avec l'adulte.
+narrateur|Lila s'assoit déjà sur la chaise. Les fesses sont sur l'assise. Les pieds sont par terre. Les mains tiennent le doudou. Papa est l'adulte, tout près. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pense au bac à sable. Papa attache la ceinture. Lila reste assise. Fesses sur le siège. Avec l'adulte. Les arbres défilent. Lila chante, assise. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1867,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la voiture, on est comment ?</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2044,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est restée assise. Avec l'adulte. Fesses sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2235,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2357,6 +2406,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend les cubes. Le sol est un peu frais. Lila tient les cubes, assise. Avec l'adulte. Les fesses ne bougent pas. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2599,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2713,6 +2772,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. La lumière est claire. On essuie une miette. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2939,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3110,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Des miettes dorment sur la table. On met le doudou près. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3277,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3448,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Un chat miaule une fois. On lace les chaussures. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3615,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3786,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend le livre. Le bois sent le chaud. Le livre est sur les genoux. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3887,6 +3981,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3911,7 +4010,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton rouge. Les chaussures font toc toc. On met le manteau. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range. Papa dit : c'est bien.</t>
+          <t>Lila pose un jeton rouge. Les chaussures font toc toc. On met le manteau. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4053,6 +4152,14 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Les chaussures font toc toc. On met le manteau. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4322,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4493,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. La couverture est douce. On boit une gorgée. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4660,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4831,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Une cloche tinte au loin. On feuillette le livre. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4998,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5169,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend la dînette. Un pigeon roucoule. La dînette attend plus tard. Maintenant, assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5225,6 +5362,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5393,6 +5535,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Le bois sent le chaud. On referme le livre. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5555,6 +5702,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5579,7 +5731,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton bleu. Une goutte tombe, ploc. On pose le ballon. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+          <t>Lila pose un jeton bleu. Une goutte tombe, ploc. On pose le ballon. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5721,6 +5873,13 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Une goutte tombe, ploc. On pose le ballon. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5883,6 +6042,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6049,6 +6213,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Le savon sent la fleur. On secoue le sable. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6211,6 +6380,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6235,7 +6409,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila pense au toboggan. Le dos est contre le dossier. On reste assis, avec l'adulte. Les mains sont sur le doudou. Papa dit : tes fesses restent sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
+          <t>Lila pense au toboggan. Le dos est contre le dossier. On reste assis, avec l'adulte. Les mains sont sur le doudou. Tes fesses restent sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6377,6 +6551,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pense au toboggan. Le dos est contre le dossier. On reste assis, avec l'adulte. Les mains sont sur le doudou.
+papa|Tes fesses restent sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6561,6 +6741,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Qui est avec toi, assis devant ?</t>
         </is>
       </c>
     </row>
@@ -6733,6 +6918,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le dos contre le dossier. Assis, avec papa. L'adulte est là. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6919,6 +7109,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7085,6 +7280,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend les cubes. L'eau fait un petit bruit. Un cube dans la main. Lila est assise. Papa conduit. Avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7275,6 +7475,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7299,7 +7504,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton rouge. Le tissu est tout doux. On caresse le tissu. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range. Papa dit : c'est bien.</t>
+          <t>Lila pose un jeton rouge. Le tissu est tout doux. On caresse le tissu. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7441,6 +7646,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Le tissu est tout doux. On caresse le tissu. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7603,6 +7814,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7769,6 +7985,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Une cuillère tinte. On tend la main. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7931,6 +8152,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7955,7 +8181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton vert. Le sable est tiède. On chante un petit air. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+          <t>Lila pose un jeton vert. Le sable est tiède. On chante un petit air. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8097,6 +8323,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Le sable est tiède. On chante un petit air. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8259,6 +8492,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8425,6 +8663,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend le livre. La terre est un peu humide. Lila tourne une page, assise. Avec l'adulte. Fesses sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8613,6 +8856,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8781,6 +9029,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Un rire court, tout petit. On compte jusqu'à trois. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8943,6 +9196,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9109,6 +9367,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Le papier froisse, chut. On montre du doigt. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9271,6 +9534,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9437,6 +9705,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. L'herbe chatouille le mollet. On range la chaise. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9599,6 +9872,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9765,6 +10043,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend la dînette. Un vélo passe, toc toc. Une petite tasse imaginaire. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9955,6 +10238,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9979,7 +10267,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton rouge. Un pigeon roucoule. On range un objet. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range. Papa dit : c'est bien.</t>
+          <t>Lila pose un jeton rouge. Un pigeon roucoule. On range un objet. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10121,6 +10409,14 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Un pigeon roucoule. On range un objet. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10283,6 +10579,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10449,6 +10750,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. La fenêtre vibre un peu. On se tient la main. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10611,6 +10917,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10777,6 +11088,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Le lait est froid dans le verre. On dit merci. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10939,6 +11255,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11105,6 +11426,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pense aux balançoires. Les pieds sont sur le tapis. Lila est assise, avec l'adulte. La ceinture est là. Papa sourit. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11285,6 +11611,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les fesses sont où ?</t>
         </is>
       </c>
     </row>
@@ -11457,6 +11788,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sur le tapis. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11643,6 +11979,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11809,6 +12150,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend les cubes. Le sol est un peu frais. Les cubes dorment dans le sac. Lila assise. Avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11997,6 +12343,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12165,6 +12516,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. La corde du sac est rêche. On souffle doucement. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12327,6 +12683,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12351,7 +12712,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton bleu. Le savon mousse entre les doigts. On écoute jusqu'au bout. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+          <t>Lila pose un jeton bleu. Le savon mousse entre les doigts. On écoute jusqu'au bout. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12493,6 +12854,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Le savon mousse entre les doigts. On écoute jusqu'au bout. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12655,6 +13023,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12821,6 +13194,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Un ruisseau chante. On attend son tour. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12983,6 +13361,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13149,6 +13532,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend le livre. La corde du sac est rêche. Le livre se ferme. On reste assis, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13339,6 +13727,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13363,7 +13756,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton rouge. La laine gratte un peu. On sourit ensemble. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range. Papa dit : c'est bien.</t>
+          <t>Lila pose un jeton rouge. La laine gratte un peu. On sourit ensemble. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13505,6 +13898,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. La laine gratte un peu. On sourit ensemble. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13667,6 +14066,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13833,6 +14237,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Un pain croustille. On pose les pieds par terre. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13995,6 +14404,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14019,7 +14433,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Lila pose un jeton vert. Le savon glisse. On parle tout bas. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte a dit : on s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+          <t>Lila pose un jeton vert. Le savon glisse. On parle tout bas. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte On s'arrête. Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14161,6 +14575,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Le savon glisse. On parle tout bas. On est resté assis, avec l'adulte. Fesses sur le siège. L'adulte
+enfant-f|On s'arrête.
+narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14323,6 +14744,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14489,6 +14915,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila prend la dînette. Un chat miaule une fois. Lila pose les mains. Assis. Avec l'adulte. La ceinture est là. On reste assis, fesses sur le siège, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14677,6 +15108,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14845,6 +15281,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton rouge. Une plume vole. On range les jouets. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15007,6 +15448,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15173,6 +15619,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton bleu. Le banc est lisse. On s'assoit un moment. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15335,6 +15786,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15501,6 +15957,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose un jeton vert. Un grelot sonne. On respire, un, deux. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15663,6 +16124,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15681,7 +16147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15754,6 +16220,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-002.xlsx
+++ b/stories/arbres/TREE-SOC-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Lila s'assoit déjà sur la chaise. Les fesses sont sur l'assise. Les pieds sont par terre. Les mains tiennent le doudou. Papa est l'adulte, tout près. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
           <t>narrateur|Lila pense au bac à sable. Papa attache la ceinture. Lila reste assise. Fesses sur le siège. Avec l'adulte. Les arbres défilent. Lila chante, assise. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1874,6 +1882,7 @@
           <t>narrateur|Dans la voiture, on est comment ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2049,6 +2058,7 @@
           <t>narrateur|Lila est restée assise. Avec l'adulte. Fesses sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2240,6 +2250,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2411,6 +2422,7 @@
           <t>narrateur|Lila prend les cubes. Le sol est un peu frais. Lila tient les cubes, assise. Avec l'adulte. Les fesses ne bougent pas. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2606,6 +2618,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2777,6 +2790,7 @@
           <t>narrateur|Lila pose un jeton rouge. La lumière est claire. On essuie une miette. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2944,6 +2958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3115,6 +3130,7 @@
           <t>narrateur|Lila pose un jeton bleu. Des miettes dorment sur la table. On met le doudou près. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3282,6 +3298,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3453,6 +3470,7 @@
           <t>narrateur|Lila pose un jeton vert. Un chat miaule une fois. On lace les chaussures. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3620,6 +3638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3791,6 +3810,7 @@
           <t>narrateur|Lila prend le livre. Le bois sent le chaud. Le livre est sur les genoux. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3986,6 +4006,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4160,6 +4181,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4327,6 +4349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4498,6 +4521,7 @@
           <t>narrateur|Lila pose un jeton bleu. La couverture est douce. On boit une gorgée. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4665,6 +4689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4836,6 +4861,7 @@
           <t>narrateur|Lila pose un jeton vert. Une cloche tinte au loin. On feuillette le livre. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5003,6 +5029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5174,6 +5201,7 @@
           <t>narrateur|Lila prend la dînette. Un pigeon roucoule. La dînette attend plus tard. Maintenant, assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5369,6 +5397,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5540,6 +5569,7 @@
           <t>narrateur|Lila pose un jeton rouge. Le bois sent le chaud. On referme le livre. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5707,6 +5737,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5880,6 +5911,7 @@
 narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6047,6 +6079,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6218,6 +6251,7 @@
           <t>narrateur|Lila pose un jeton vert. Le savon sent la fleur. On secoue le sable. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6385,6 +6419,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6557,6 +6592,7 @@
 papa|Tes fesses restent sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6748,6 +6784,7 @@
           <t>narrateur|Qui est avec toi, assis devant ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6923,6 +6960,7 @@
           <t>narrateur|Le dos contre le dossier. Assis, avec papa. L'adulte est là. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7114,6 +7152,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7285,6 +7324,7 @@
           <t>narrateur|Lila prend les cubes. L'eau fait un petit bruit. Un cube dans la main. Lila est assise. Papa conduit. Avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7480,6 +7520,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7652,6 +7693,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7819,6 +7861,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7990,6 +8033,7 @@
           <t>narrateur|Lila pose un jeton bleu. Une cuillère tinte. On tend la main. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8157,6 +8201,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8330,6 +8375,7 @@
 narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8497,6 +8543,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8668,6 +8715,7 @@
           <t>narrateur|Lila prend le livre. La terre est un peu humide. Lila tourne une page, assise. Avec l'adulte. Fesses sur le siège. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8863,6 +8911,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9034,6 +9083,7 @@
           <t>narrateur|Lila pose un jeton rouge. Un rire court, tout petit. On compte jusqu'à trois. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9201,6 +9251,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9372,6 +9423,7 @@
           <t>narrateur|Lila pose un jeton bleu. Le papier froisse, chut. On montre du doigt. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9539,6 +9591,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9710,6 +9763,7 @@
           <t>narrateur|Lila pose un jeton vert. L'herbe chatouille le mollet. On range la chaise. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9877,6 +9931,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10048,6 +10103,7 @@
           <t>narrateur|Lila prend la dînette. Un vélo passe, toc toc. Une petite tasse imaginaire. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10243,6 +10299,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10417,6 +10474,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10584,6 +10642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10755,6 +10814,7 @@
           <t>narrateur|Lila pose un jeton bleu. La fenêtre vibre un peu. On se tient la main. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10922,6 +10982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11093,6 +11154,7 @@
           <t>narrateur|Lila pose un jeton vert. Le lait est froid dans le verre. On dit merci. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11260,6 +11322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11431,6 +11494,7 @@
           <t>narrateur|Lila pense aux balançoires. Les pieds sont sur le tapis. Lila est assise, avec l'adulte. La ceinture est là. Papa sourit. On reste assis. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11618,6 +11682,7 @@
           <t>narrateur|Les fesses sont où ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11793,6 +11858,7 @@
           <t>narrateur|Les pieds sur le tapis. Lila reste assise, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11984,6 +12050,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12155,6 +12222,7 @@
           <t>narrateur|Lila prend les cubes. Le sol est un peu frais. Les cubes dorment dans le sac. Lila assise. Avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12350,6 +12418,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12521,6 +12590,7 @@
           <t>narrateur|Lila pose un jeton rouge. La corde du sac est rêche. On souffle doucement. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12688,6 +12758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12861,6 +12932,7 @@
 narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13028,6 +13100,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13199,6 +13272,7 @@
           <t>narrateur|Lila pose un jeton vert. Un ruisseau chante. On attend son tour. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13366,6 +13440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13537,6 +13612,7 @@
           <t>narrateur|Lila prend le livre. La corde du sac est rêche. Le livre se ferme. On reste assis, avec l'adulte. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13732,6 +13808,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13904,6 +13981,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14071,6 +14149,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14242,6 +14321,7 @@
           <t>narrateur|Lila pose un jeton bleu. Un pain croustille. On pose les pieds par terre. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. On souffle. Lila sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14409,6 +14489,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14582,6 +14663,7 @@
 narrateur|Puis on descend ensemble. On reste assis, fesses sur le siège, avec l'adulte. Lila prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14749,6 +14831,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14920,6 +15003,7 @@
           <t>narrateur|Lila prend la dînette. Un chat miaule une fois. Lila pose les mains. Assis. Avec l'adulte. La ceinture est là. On reste assis, fesses sur le siège, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15115,6 +15199,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15286,6 +15371,7 @@
           <t>narrateur|Lila pose un jeton rouge. Une plume vole. On range les jouets. On est resté assis, avec l'adulte. Fesses sur le siège. La ceinture est restée fermée. On reste assis, fesses sur le siège, avec l'adulte. Lila dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15453,6 +15539,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15624,6 +15711,7 @@
           <t>narrateur|Lila pose un jeton bleu. Le banc est lisse. On s'assoit un moment. On est resté assis, avec l'adulte. Fesses sur le siège. Les pieds étaient sur le tapis. On reste assis, fesses sur le siège, avec l'adulte. Papa serre Lila tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15791,6 +15879,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15962,6 +16051,7 @@
           <t>narrateur|Lila pose un jeton vert. Un grelot sonne. On respire, un, deux. On est resté assis, avec l'adulte. Fesses sur le siège. Les mains tenaient le doudou. On reste assis, fesses sur le siège, avec l'adulte. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16129,6 +16219,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16147,7 +16238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16227,6 +16318,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16428,6 +16533,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
